--- a/output/tablas/analisis_eventos_y_alarmas.xlsx
+++ b/output/tablas/analisis_eventos_y_alarmas.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="18" windowWidth="16098" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="18" windowWidth="16098" windowHeight="9660" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="eventos" sheetId="1" r:id="rId1"/>
@@ -13014,6 +13014,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="3" max="3" width="33.26171875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1015625" customWidth="1"/>
+    <col min="5" max="5" width="24.05078125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.83984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.9453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.68359375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5234375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.83984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
